--- a/data/agriculture_requests.xlsx
+++ b/data/agriculture_requests.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46303.71153272584</v>
+        <v>46303.71153273148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,10 +603,8 @@
           <t>Deiseal</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="J2" t="n">
+        <v>50</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -656,6 +654,99 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AR-2026-27-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46312.70839807174</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PESTICIDE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Allice</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DG22001</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>YSA management</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Scouting reports shows high levels of YSA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
